--- a/samples/test_data.xlsx
+++ b/samples/test_data.xlsx
@@ -413,14 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,103 +458,4045 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0012345678</t>
+          <t>1000000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25000000</t>
+          <t>15175000</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Tehran</t>
+          <t>Tehran, Block 1, Unit 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Maryam Ahmadi</t>
+          <t>Maryam Moradi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0098765432</t>
+          <t>1000000002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>31500000</t>
+          <t>15350000</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Shiraz</t>
+          <t>Shiraz, Block 2, Unit 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sara Karimi</t>
+          <t>Sara Shams</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0055512345</t>
+          <t>1000000003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18750000</t>
+          <t>15525000</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tabriz</t>
+          <t>Tabriz, Block 3, Unit 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hossein Moradi</t>
+          <t>Hossein Nikoo</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0044499991</t>
+          <t>1000000004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>15700000</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 4, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1000000005</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>15875000</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 5, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1000000006</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>16050000</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Karaj, Block 6, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1000000007</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>16225000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Qom, Block 7, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1000000008</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>16400000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 8, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1000000009</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>16575000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Tehran, Block 9, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1000000010</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>16750000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 10, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1000000011</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>16925000</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 11, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1000000012</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>42000000</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Mashhad</t>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>17100000</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 12, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1000000013</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>17275000</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 13, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1000000014</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>17450000</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Karaj, Block 14, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1000000015</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>17625000</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Qom, Block 15, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000000016</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>17800000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 16, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1000000017</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>17975000</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Tehran, Block 17, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1000000018</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>18150000</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 18, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1000000019</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>18325000</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 19, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1000000020</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>18500000</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 20, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1000000021</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>18675000</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 1, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1000000022</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>18850000</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Karaj, Block 2, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1000000023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>19025000</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Qom, Block 3, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1000000024</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>19200000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 4, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1000000025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>19375000</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Tehran, Block 5, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1000000026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>19550000</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 6, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1000000027</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>19725000</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 7, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1000000028</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>19900000</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 8, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1000000029</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>20075000</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 9, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1000000030</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>20250000</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Karaj, Block 10, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1000000031</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>20425000</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Qom, Block 11, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1000000032</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>20600000</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 12, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1000000033</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>20775000</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Tehran, Block 13, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1000000034</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>20950000</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 14, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1000000035</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>21125000</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 15, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1000000036</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>21300000</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 16, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1000000037</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>21475000</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 17, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1000000038</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>21650000</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Karaj, Block 18, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1000000039</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>21825000</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Qom, Block 19, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1000000040</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22000000</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 20, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1000000041</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22175000</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Tehran, Block 1, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1000000042</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22350000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 2, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1000000043</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22525000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 3, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1000000044</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22700000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 4, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1000000045</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22875000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 5, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1000000046</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>23050000</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Karaj, Block 6, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1000000047</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>23225000</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Qom, Block 7, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1000000048</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>23400000</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 8, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1000000049</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>23575000</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Tehran, Block 9, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1000000050</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>23750000</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 10, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1000000051</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>23925000</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 11, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1000000052</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>24100000</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 12, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1000000053</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>24275000</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 13, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1000000054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>24450000</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Karaj, Block 14, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1000000055</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>24625000</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Qom, Block 15, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1000000056</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>24800000</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 16, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1000000057</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>24975000</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Tehran, Block 17, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1000000058</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>25150000</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 18, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1000000059</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>25325000</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 19, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1000000060</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>25500000</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 20, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1000000061</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>25675000</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 1, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1000000062</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>25850000</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Karaj, Block 2, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1000000063</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>26025000</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Qom, Block 3, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1000000064</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>26200000</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 4, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1000000065</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>26375000</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Tehran, Block 5, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1000000066</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>26550000</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 6, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1000000067</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>26725000</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 7, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1000000068</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>26900000</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 8, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>1000000069</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>27075000</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 9, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>1000000070</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>27250000</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Karaj, Block 10, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>1000000071</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>27425000</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Qom, Block 11, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>1000000072</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>27600000</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 12, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1000000073</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>27775000</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Tehran, Block 13, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>1000000074</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>27950000</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 14, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>1000000075</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>28125000</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 15, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>1000000076</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>28300000</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 16, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>1000000077</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>28475000</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 17, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>1000000078</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>28650000</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Karaj, Block 18, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>1000000079</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>28825000</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Qom, Block 19, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1000000080</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>29000000</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 20, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>1000000081</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>29175000</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Tehran, Block 1, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>1000000082</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>29350000</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 2, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>1000000083</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>29525000</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 3, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1000000084</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>29700000</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 4, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>1000000085</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>29875000</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 5, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1000000086</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>30050000</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Karaj, Block 6, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1000000087</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>30225000</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Qom, Block 7, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1000000088</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>30400000</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 8, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>1000000089</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>30575000</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Tehran, Block 9, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1000000090</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>30750000</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 10, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>1000000091</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>30925000</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 11, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1000000092</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>31100000</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 12, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1000000093</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>31275000</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 13, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1000000094</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>31450000</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Karaj, Block 14, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1000000095</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>31625000</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Qom, Block 15, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1000000096</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>31800000</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 16, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1000000097</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>31975000</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Tehran, Block 17, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1000000098</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>32150000</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 18, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>1000000099</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>32325000</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 19, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>1000000100</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>32500000</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 20, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1000000101</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>32675000</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 1, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1000000102</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>32850000</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Karaj, Block 2, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1000000103</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>33025000</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Qom, Block 3, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1000000104</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>33200000</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 4, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1000000105</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>33375000</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Tehran, Block 5, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>1000000106</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>33550000</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 6, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>1000000107</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>33725000</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 7, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>1000000108</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>33900000</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 8, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>1000000109</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>34075000</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 9, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1000000110</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>34250000</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Karaj, Block 10, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1000000111</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>34425000</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Qom, Block 11, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>1000000112</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>34600000</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 12, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1000000113</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>34775000</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Tehran, Block 13, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1000000114</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>34950000</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 14, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>1000000115</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>35125000</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 15, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1000000116</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>35300000</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 16, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>1000000117</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>35475000</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 17, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1000000118</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>35650000</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Karaj, Block 18, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1000000119</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>35825000</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Qom, Block 19, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1000000120</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>36000000</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 20, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>1000000121</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>36175000</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Tehran, Block 1, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1000000122</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>36350000</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 2, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1000000123</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>36525000</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 3, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1000000124</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>36700000</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 4, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>1000000125</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>36875000</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 5, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1000000126</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>37050000</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Karaj, Block 6, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1000000127</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>37225000</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Qom, Block 7, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>1000000128</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>37400000</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 8, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>1000000129</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>37575000</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Tehran, Block 9, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1000000130</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>37750000</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 10, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>1000000131</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>37925000</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 11, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1000000132</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>38100000</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 12, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1000000133</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>38275000</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 13, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>1000000134</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>38450000</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Karaj, Block 14, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>1000000135</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>38625000</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Qom, Block 15, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>1000000136</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>38800000</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 16, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>1000000137</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>38975000</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Tehran, Block 17, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>1000000138</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>39150000</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 18, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>1000000139</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>39325000</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 19, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>1000000140</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>39500000</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 20, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Ali Rezaei</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>1000000141</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>39675000</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 1, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Maryam Moradi</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>1000000142</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>39850000</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Karaj, Block 2, Unit 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Sara Shams</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>1000000143</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>40025000</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Qom, Block 3, Unit 7</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Hossein Nikoo</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>1000000144</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>40200000</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Ahvaz, Block 4, Unit 8</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Reza Karimi</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>1000000145</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>40375000</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Tehran, Block 5, Unit 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Niloofar Jafari</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1000000146</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>40550000</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Shiraz, Block 6, Unit 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Mehdi Mohammadi</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1000000147</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>40725000</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Tabriz, Block 7, Unit 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Parisa Ahmadi</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1000000148</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>40900000</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Mashhad, Block 8, Unit 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Amir Hosseini</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1000000149</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>41075000</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Isfahan, Block 9, Unit 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Fatemeh Rahimi</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1000000150</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>41250000</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Karaj, Block 10, Unit 6</t>
         </is>
       </c>
     </row>
